--- a/artfynd/A 172-2021 artfynd.xlsx
+++ b/artfynd/A 172-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1802,360 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114729913</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56449</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Annevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>599058</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7180494</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114729910</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57232</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Annevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>599119</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7180454</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114729911</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Annevare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599060</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7180498</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 172-2021 artfynd.xlsx
+++ b/artfynd/A 172-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 172-2021 artfynd.xlsx
+++ b/artfynd/A 172-2021 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>118328991</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>96892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
